--- a/results/Int Task Remove ACC 0.8/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.8/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.03566858117972497</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01075425857907069</v>
+        <v>0.01074327250722828</v>
       </c>
       <c r="F3" t="n">
         <v>0.007669154131302652</v>
@@ -1169,22 +1169,22 @@
         <v>0.01999164769228568</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003708689610451632</v>
+        <v>0.0003707283852466925</v>
       </c>
       <c r="J3" t="n">
         <v>0.0001141367904028702</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004116812770228813</v>
+        <v>0.004111470889886932</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004116681937307463</v>
+        <v>0.004122023817649344</v>
       </c>
       <c r="M3" t="n">
         <v>-0.0008880814861301556</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01827306755819858</v>
+        <v>0.01826219490678731</v>
       </c>
       <c r="O3" t="n">
         <v>0.03202918670814693</v>
@@ -1208,7 +1208,7 @@
         <v>0.320903605846772</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0003762108413870435</v>
+        <v>0.0003653865049048122</v>
       </c>
       <c r="W3" t="n">
         <v>0.0008493496004880974</v>
@@ -1232,13 +1232,13 @@
         <v>0.05930088801377746</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1034941689522006</v>
+        <v>0.103489257360845</v>
       </c>
       <c r="AE3" t="n">
         <v>0.2850408579159164</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1145136297542223</v>
+        <v>0.1145185413455779</v>
       </c>
       <c r="AG3" t="n">
         <v>0.03918360315553184</v>
@@ -1262,7 +1262,7 @@
         <v>0.0001282614821082806</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0008575138079892641</v>
+        <v>-0.0008627908528441458</v>
       </c>
       <c r="AO3" t="n">
         <v>0.3688074807239504</v>
@@ -1428,7 +1428,7 @@
         <v>0.03320857174484992</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02575451345889612</v>
+        <v>0.02573845534919193</v>
       </c>
       <c r="F4" t="n">
         <v>0.01359669961128567</v>
@@ -1440,22 +1440,22 @@
         <v>0.03218943610913026</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00106212590252601</v>
+        <v>0.001066204550928237</v>
       </c>
       <c r="J4" t="n">
         <v>0.006668884466676244</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01844036850808825</v>
+        <v>0.01843884706657604</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01845001254493225</v>
+        <v>0.01845153138951163</v>
       </c>
       <c r="M4" t="n">
         <v>0.009616706541883046</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03410971569861304</v>
+        <v>0.03410950932396781</v>
       </c>
       <c r="O4" t="n">
         <v>0.03462936514697155</v>
@@ -1479,7 +1479,7 @@
         <v>0.1038058948488775</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001061082768064816</v>
+        <v>0.001067212188444502</v>
       </c>
       <c r="W4" t="n">
         <v>0.001553952408677168</v>
@@ -1503,13 +1503,13 @@
         <v>0.05704600731761795</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.08265222532311856</v>
+        <v>0.08266313922621797</v>
       </c>
       <c r="AE4" t="n">
         <v>0.132984896748488</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.07315793204175323</v>
+        <v>0.07314839051776052</v>
       </c>
       <c r="AG4" t="n">
         <v>0.04965920517345227</v>
@@ -1533,7 +1533,7 @@
         <v>0.001246732800150878</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.01892048354995749</v>
+        <v>0.01891958736680303</v>
       </c>
       <c r="AO4" t="n">
         <v>0.09964425203647592</v>
@@ -1774,13 +1774,13 @@
         <v>-0.04400785854616892</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.06178781925343809</v>
+        <v>-0.06183693516699409</v>
       </c>
       <c r="AE5" t="n">
         <v>-0.01463654223968563</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01340864440078581</v>
+        <v>-0.01335952848722981</v>
       </c>
       <c r="AG5" t="n">
         <v>-0.004578313253012045</v>
@@ -1970,7 +1970,7 @@
         <v>0.0100677751089875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001274498780978533</v>
+        <v>0.00128677775936753</v>
       </c>
       <c r="F6" t="n">
         <v>0.003833967711642575</v>
@@ -1982,7 +1982,7 @@
         <v>0.001490549624825449</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0004221762636790083</v>
+        <v>-0.000463294684731641</v>
       </c>
       <c r="J6" t="n">
         <v>-0.0007512636297167473</v>
@@ -1997,7 +1997,7 @@
         <v>-0.001435711800947431</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.001643506146445711</v>
+        <v>-0.001683591662212683</v>
       </c>
       <c r="O6" t="n">
         <v>0.0007187241495191677</v>
@@ -2021,7 +2021,7 @@
         <v>0.243158843086199</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0004221762636790083</v>
+        <v>-0.000463294684731641</v>
       </c>
       <c r="W6" t="n">
         <v>-0.0001803540373060686</v>
@@ -2241,7 +2241,7 @@
         <v>0.03176677196252293</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01264029930518439</v>
+        <v>0.01261357562800641</v>
       </c>
       <c r="F7" t="n">
         <v>0.005700630566819798</v>
@@ -2253,7 +2253,7 @@
         <v>0.0289010765264869</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001068518823061804</v>
+        <v>0.000133561284015582</v>
       </c>
       <c r="J7" t="n">
         <v>0.000913671497229479</v>
@@ -2268,7 +2268,7 @@
         <v>2.28081200822738e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003788325062532194</v>
+        <v>0.003788325062532199</v>
       </c>
       <c r="O7" t="n">
         <v>0.03336799417104064</v>
@@ -2292,7 +2292,7 @@
         <v>0.3302743104886905</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000133561284015582</v>
+        <v>0.0001068518823061804</v>
       </c>
       <c r="W7" t="n">
         <v>0.000484968881771164</v>
@@ -2530,10 +2530,10 @@
         <v>0.00227563685012227</v>
       </c>
       <c r="K8" t="n">
+        <v>0.00899316457352169</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.009006519274376391</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.00899316457352169</v>
       </c>
       <c r="M8" t="n">
         <v>0.001050088786459127</v>
@@ -2617,7 +2617,7 @@
         <v>0.000802598147692804</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001765005135425385</v>
+        <v>0.001725427299013776</v>
       </c>
       <c r="AO8" t="n">
         <v>0.422362323164687</v>
@@ -2783,7 +2783,7 @@
         <v>0.09939192924267551</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04210526315789476</v>
+        <v>0.04205315268368944</v>
       </c>
       <c r="F9" t="n">
         <v>0.02609649122807015</v>
